--- a/Results_isofys/test.xlsx
+++ b/Results_isofys/test.xlsx
@@ -4933,18 +4933,14 @@
         <v>0.4786645153959252</v>
       </c>
       <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>p11-5785</t>
-        </is>
-      </c>
-      <c r="I99" t="n">
+      <c r="H99" t="n">
         <v>1.37</v>
       </c>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="n">
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="n">
         <v>-33.6</v>
       </c>
+      <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
@@ -4982,18 +4978,14 @@
         <v>0.4869895502488357</v>
       </c>
       <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>p11-7887</t>
-        </is>
-      </c>
-      <c r="I100" t="n">
+      <c r="H100" t="n">
         <v>1.88</v>
       </c>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="n">
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="n">
         <v>-33.5</v>
       </c>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
